--- a/output/Bewertungsmatrix.xlsx
+++ b/output/Bewertungsmatrix.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\DSI\Abschlussprojekt\Datei Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAE0A41-4F80-481F-A3F9-6DD71A35B439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D6031B-B3AE-4E0A-9F91-0B344FABE31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4FCBAF38-7CEA-45CF-AE17-81E5D47316D2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4FCBAF38-7CEA-45CF-AE17-81E5D47316D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tag 9" sheetId="2" r:id="rId1"/>
+    <sheet name="Tag 8" sheetId="3" r:id="rId2"/>
+    <sheet name="Tag 6" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="163">
   <si>
     <t>Methode</t>
   </si>
@@ -114,13 +116,588 @@
   </si>
   <si>
     <t>Granularity</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Generisch</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>~11.7%</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>Segment-Ansprache</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>~25%</t>
+  </si>
+  <si>
+    <t>Individuelles Modell</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>(noch offen)</t>
+  </si>
+  <si>
+    <t>Generisch (Baseline)</t>
+  </si>
+  <si>
+    <t>Segmentierung (Cluster)</t>
+  </si>
+  <si>
+    <t>~25.6%</t>
+  </si>
+  <si>
+    <t>Segment-basierte Ansprache</t>
+  </si>
+  <si>
+    <t>~2.4x Lift</t>
+  </si>
+  <si>
+    <t>1. Performance (woher kommen 11.7%, 25%, 2.4x?)</t>
+  </si>
+  <si>
+    <t>Was ich dort gesehen habe:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Baseline (Control): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>11.7%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experienced: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>25.6%</t>
+    </r>
+  </si>
+  <si>
+    <t>Mass Market: ~10%</t>
+  </si>
+  <si>
+    <t>Daraus:</t>
+  </si>
+  <si>
+    <t>Wert</t>
+  </si>
+  <si>
+    <t>Bedeutung</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>generisch</t>
+  </si>
+  <si>
+    <t>segmentiert</t>
+  </si>
+  <si>
+    <t>2.4x</t>
+  </si>
+  <si>
+    <t>Lift</t>
+  </si>
+  <si>
+    <t>2. Granularity (0.2 / 0.6)</t>
+  </si>
+  <si>
+    <t>Was ich gesehen habe:</t>
+  </si>
+  <si>
+    <t>klare Cluster:</t>
+  </si>
+  <si>
+    <t>Experienced</t>
+  </si>
+  <si>
+    <t>Mass Market</t>
+  </si>
+  <si>
+    <t>Champions etc.</t>
+  </si>
+  <si>
+    <t>bedeutet:</t>
+  </si>
+  <si>
+    <t>Nutzer werden in Gruppen eingeteilt</t>
+  </si>
+  <si>
+    <t>KEINE individuelle Entscheidung</t>
+  </si>
+  <si>
+    <t>daraus:</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>3. Data Volume (0.5 / 0.6)</t>
+  </si>
+  <si>
+    <t>Features, die sichtbar sind:</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>campaign</t>
+  </si>
+  <si>
+    <t>previous</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>Das sind:</t>
+  </si>
+  <si>
+    <t>mehrere Variablen</t>
+  </si>
+  <si>
+    <t>gemischte Datentypen</t>
+  </si>
+  <si>
+    <t>Bewertung</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">→ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>mittel = 0.5–0.6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">nicht wenig → 0.2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicht extrem viele → 0.9 </t>
+  </si>
+  <si>
+    <t>4. Sensitivity (0.5–0.6)</t>
+  </si>
+  <si>
+    <t>Bewertung der Features:</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Sensitivität</t>
+  </si>
+  <si>
+    <t>clicks / behaviour</t>
+  </si>
+  <si>
+    <t>mittel–hoch</t>
+  </si>
+  <si>
+    <t>Gesamt: gemischt → mittel</t>
+  </si>
+  <si>
+    <t>deshalb:</t>
+  </si>
+  <si>
+    <t>Ansprache</t>
+  </si>
+  <si>
+    <t>5. Warum Segment vs Ansprache leicht unterschiedlich</t>
+  </si>
+  <si>
+    <t>gleiche Daten, aber:</t>
+  </si>
+  <si>
+    <t>Segmentierung = Analyse</t>
+  </si>
+  <si>
+    <t>Ansprache = Anwendung</t>
+  </si>
+  <si>
+    <t>Faktor</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>1. Was heute neu dazukommt</t>
+  </si>
+  <si>
+    <t>Ich verbessere 3 Dinge:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">statt pauschal jetzt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>feature-basiert denken</t>
+    </r>
+  </si>
+  <si>
+    <t>bisher fehlt individuelle Modelle (Granularity = 0.9)</t>
+  </si>
+  <si>
+    <t>klare Logik zwischen:</t>
+  </si>
+  <si>
+    <t>Modell</t>
+  </si>
+  <si>
+    <t>Risiko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTPUT </t>
+  </si>
+  <si>
+    <t>Erste Anwendung des Risk Score auf empirische Ergebnisse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Rahmen der Analyse wurden die Ergebnisse der Segmentierung und der darauf basierenden Personalisierungslogik erstmals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">in die entwickelte Bewertungsmatrix überführt. Dabei zeigt sich, dass segmentbasierte Ansätze ein mittleres Profiling-Level </t>
+  </si>
+  <si>
+    <t>aufweisen und mit einem moderaten Risk Score (ca. 0.53–0.60) verbunden sind.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleichzeitig konnte ein deutlicher deutlicher Performance-Anstieg beobachtet werden: Die Response-Rate steigt von etwa 11.7% in der </t>
+  </si>
+  <si>
+    <t>generischen Ansprache auf über 25% in segmentierten Zielgruppen. Dies entspricht einem signifikanten Lift, der die Hypothese H1 unterstützt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Ergebnisse deuten darauf hin, dass Personalisierung auf Segmentebene einen effizienten Kompromiss zwischen Performance-Steigerung </t>
+  </si>
+  <si>
+    <t>und Datenschutzrisiko darstellt. Eine kritische Schwelle, bei der das Risiko den Nutzen übersteigt, ist auf dieser Ebene noch nicht erreicht.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmentierung beschreibt die analytische Gruppierung von Nutzern auf Basis ihrer Merkmale und Verhaltensweisen, während </t>
+  </si>
+  <si>
+    <t xml:space="preserve">segmentbasierte Ansprache die operative Nutzung dieser Gruppen zur gezielten Ausspielung von Marketingmaßnahmen darstellt. </t>
+  </si>
+  <si>
+    <t>Letztere weist aufgrund der direkten Einflussnahme auf Nutzerverhalten eine höhere Eingriffsintensität und damit ein erhöhtes Datenschutzrisiko auf.</t>
+  </si>
+  <si>
+    <t>Sensitivity genauer machen (wichtig!)</t>
+  </si>
+  <si>
+    <t>High-Risk-Level ergänzen</t>
+  </si>
+  <si>
+    <t>Matrix konsistent machen</t>
+  </si>
+  <si>
+    <t>2. Verfeinerte Bewertung (auf Basis deiner Daten)</t>
+  </si>
+  <si>
+    <t>Methode 1: Generisch</t>
+  </si>
+  <si>
+    <r>
+      <t>è</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>bleibt gleich</t>
+    </r>
+  </si>
+  <si>
+    <t>Methode 2: Segmentierung</t>
+  </si>
+  <si>
+    <r>
+      <t>J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>etzt sauber begründet:</t>
+    </r>
+  </si>
+  <si>
+    <t>Features:</t>
+  </si>
+  <si>
+    <t>age (mittel)</t>
+  </si>
+  <si>
+    <t>balance (mittel)</t>
+  </si>
+  <si>
+    <t>campaign (niedrig)</t>
+  </si>
+  <si>
+    <t>Bewertung:</t>
+  </si>
+  <si>
+    <t>Begründung</t>
+  </si>
+  <si>
+    <t>mehrere Features</t>
+  </si>
+  <si>
+    <t>gemischt</t>
+  </si>
+  <si>
+    <t>Methode 3: Segment-basierte Ansprache</t>
+  </si>
+  <si>
+    <t>leicht höher:</t>
+  </si>
+  <si>
+    <t>Methode 4: Individuelle Modelle (NEU!)</t>
+  </si>
+  <si>
+    <r>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> auch wenn ich noch keine finalen Ergebnisse habe, kann ich sie </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>konzeptionell ergänzen</t>
+    </r>
+  </si>
+  <si>
+    <t>Beispiel:</t>
+  </si>
+  <si>
+    <t>individuelle Predictions</t>
+  </si>
+  <si>
+    <t>viele Features</t>
+  </si>
+  <si>
+    <t>automatisierte Entscheidung</t>
+  </si>
+  <si>
+    <t>0.6–0.7</t>
+  </si>
+  <si>
+    <r>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Risk Score ≈ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.75–0.8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Die neue Matrix </t>
+  </si>
+  <si>
+    <t>siehe oben</t>
+  </si>
+  <si>
+    <t>4. Wichtige Erkenntnis (JETZT wird H3 spannend)</t>
+  </si>
+  <si>
+    <t>Schritt</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>individuell</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <r>
+      <t>è</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Und jetzt kommt die zentrale Frage:</t>
+    </r>
+  </si>
+  <si>
+    <t>Bringt individuell wirklich so viel mehr als Segment?</t>
+  </si>
+  <si>
+    <r>
+      <t>è</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Wenn NEIN: H3 bestätigt</t>
+    </r>
+  </si>
+  <si>
+    <t>Jetzt sieht man:</t>
+  </si>
+  <si>
+    <t>5. Mein wichtigster Insight (jetzt schon!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Während segmentbasierte Personalisierung einen erheblichen Performance-Gewinn bei moderatem Risiko ermöglicht, </t>
+  </si>
+  <si>
+    <t>führt eine weitere Individualisierung zu einem deutlichen Anstieg des Datenschutzrisikos, dessen zusätzlicher Nutzen kritisch zu hinterfragen ist.</t>
+  </si>
+  <si>
+    <t>Verfeinerung der Datenschutzbewertung und Erweiterung um High-Risk-Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Rahmen der weiteren Analyse wurde die initiale Bewertungsmatrix verfeinert und um ein hohes Profiling-Level ergänzt. Dabei wurde </t>
+  </si>
+  <si>
+    <t xml:space="preserve">insbesondere die Sensitivität der verwendeten Daten differenzierter betrachtet, indem die einzelnen Features </t>
+  </si>
+  <si>
+    <t>hinsichtlich ihrer datenschutzrechtlichen Relevanz eingeordnet wurden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zusätzlich wurde ein hypothetisches Szenario für hochgradig individualisierte Modelle ergänzt, die auf individueller Ebene Vorhersagen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">treffen und automatisierte Entscheidungen ermöglichen. Diese Ansätze weisen aufgrund ihrer hohen Granularität </t>
+  </si>
+  <si>
+    <t>sowie des erweiterten Datenumfangs deutlich höhere Risk Scores auf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die erweiterte Matrix zeigt, dass der Übergang von segmentbasierter zu individueller Personalisierung mit einem überproportionalen Anstieg </t>
+  </si>
+  <si>
+    <t>des Datenschutzrisikos verbunden ist. Gleichzeitig ist der zusätzliche Nutzen in Form von Performance-Gewinnen zum aktuellen Zeitpunkt noch nicht eindeutig belegt.</t>
+  </si>
+  <si>
+    <t>Diese Beobachtung bildet die Grundlage für die weitere Analyse des Trade-offs zwischen Personalisierungsgrad und Datenschutzrisiko.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +711,31 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -143,7 +745,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -151,20 +753,105 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -349,8 +1036,357 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>140335</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>134620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5784F145-9549-966A-395E-77167813C436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="2546350"/>
+          <a:ext cx="5626735" cy="3081020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1324610</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C739D92-42A7-DE76-735E-AB0C24BD37DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="8261350"/>
+          <a:ext cx="5439410" cy="1932940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>32385</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>181610</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Grafik 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F06CD313-BD9D-414C-3CCE-E83D56B7F5F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="10287000"/>
+          <a:ext cx="5518785" cy="2023110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>128905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Grafik 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{380215B5-26CA-FBDB-76FC-9952E6EEDB68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="12496800"/>
+          <a:ext cx="5486400" cy="3811905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A666E9A-6173-8A1D-7405-3DB8E3AC09ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="19558000"/>
+          <a:ext cx="5029200" cy="4486275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1316990</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E345692C-1125-FFED-5051-E93C1A18620C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1524000" y="24161750"/>
+          <a:ext cx="5431790" cy="2606040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F836603-69FE-4736-AECC-BB521DF8291B}" name="Tabelle4" displayName="Tabelle4" ref="C4:I8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7DB130D0-EAA7-4D60-B756-B04C69FFACB2}" name="Tabelle42" displayName="Tabelle42" ref="C4:I8" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="C4:I8" xr:uid="{8F836603-69FE-4736-AECC-BB521DF8291B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4A852AD1-AEF9-4EE9-990A-474416C347BA}" name="Methode"/>
+    <tableColumn id="2" xr3:uid="{58425C2E-FFBB-4908-8DC1-2B2D6D005330}" name="Profiling-Level"/>
+    <tableColumn id="3" xr3:uid="{9CD27286-7E7B-45E6-8C21-34882B4F07FF}" name="Data Volume"/>
+    <tableColumn id="4" xr3:uid="{0A09A796-786E-4C4B-B993-322752077F3B}" name="Sensitivity"/>
+    <tableColumn id="5" xr3:uid="{59D2E8A4-0FAB-4094-A1BA-6BD7FEC96BAE}" name="Granularity"/>
+    <tableColumn id="6" xr3:uid="{F733C243-F185-4390-8DA4-55268EE3873D}" name="Risk Score"/>
+    <tableColumn id="7" xr3:uid="{BC59443A-756A-44D4-AAA8-E97C34F9BDBE}" name="Performance"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{86159070-3774-45FE-A974-F28A3E59E120}" name="Tabelle423" displayName="Tabelle423" ref="C4:I7" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="C4:I7" xr:uid="{8F836603-69FE-4736-AECC-BB521DF8291B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{344C296B-02E9-4995-80F3-38D0EDF1CB19}" name="Methode"/>
+    <tableColumn id="2" xr3:uid="{51921156-0F7E-44F4-B4C8-184CEE24D3BE}" name="Profiling-Level"/>
+    <tableColumn id="3" xr3:uid="{EC7B1C1F-8A19-4A1A-AAA1-71D8C47CE43A}" name="Data Volume"/>
+    <tableColumn id="4" xr3:uid="{E47C96B1-F412-4590-BFEF-1B097B16A608}" name="Sensitivity"/>
+    <tableColumn id="5" xr3:uid="{8B811358-C8A7-4B5A-B6EA-D53AE684B406}" name="Granularity"/>
+    <tableColumn id="6" xr3:uid="{3497741D-3545-4045-8078-9AFD077F848C}" name="Risk Score"/>
+    <tableColumn id="7" xr3:uid="{6744271E-D646-4E16-8D63-02CE35011962}" name="Performance"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F836603-69FE-4736-AECC-BB521DF8291B}" name="Tabelle4" displayName="Tabelle4" ref="C4:I8" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="C4:I8" xr:uid="{8F836603-69FE-4736-AECC-BB521DF8291B}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ABA09C39-C3E4-4085-8ACB-46D5DE0591A4}" name="Methode" dataDxfId="8"/>
@@ -681,6 +1717,1097 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0155ED-DA6F-45C9-9023-B99A2435AACE}">
+  <dimension ref="C4:I87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="9" width="19.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C11" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C12" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C13" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C14" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C15" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C16" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C17" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C18" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C19" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C20" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C21" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C23" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C24" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C25" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C29" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C30" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C31" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C32" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C33" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C34" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C35" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C36" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C38" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C41" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C42" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C43" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C44" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C46" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C47" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C48" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C49" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C50" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C51" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C52" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C53" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C54" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C55" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C56" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C57" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C58" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" ht="16" x14ac:dyDescent="0.4">
+      <c r="C60" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C63" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C64" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C65" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C66" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C67" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C68" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C69" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C70" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C71" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C73" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" ht="16" x14ac:dyDescent="0.4">
+      <c r="C74" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" ht="16" x14ac:dyDescent="0.4">
+      <c r="C75" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C77" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C78" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" ht="16" x14ac:dyDescent="0.4">
+      <c r="C79" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" ht="16" x14ac:dyDescent="0.4">
+      <c r="C80" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C81" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C82" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C83" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C84" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C85" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C86" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C87" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B04761A-003C-4A5C-A66A-238DF002FB57}">
+  <dimension ref="C4:I191"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="9" width="19.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="C5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="C7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C28" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C29" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C30" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C32" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C35" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C36" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C40" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C85" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C86" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C87" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C88" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C89" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C90" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C91" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C92" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C93" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C94" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C95" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C96" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C100" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="141" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C141" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="142" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C142" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="143" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C143" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C144" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C145" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C146" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C147" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C148" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C149" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C150" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C151" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C152" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C153" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C154" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" ht="16" x14ac:dyDescent="0.4">
+      <c r="C157" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C158" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C159" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" ht="16" x14ac:dyDescent="0.35">
+      <c r="C160" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C161" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C162" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="163" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C163" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="164" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C164" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="165" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C165" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C166" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C167" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C169" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="170" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C170" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="171" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C171" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="172" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C172" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="173" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C173" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="174" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C174" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="175" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C175" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="3:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="C176" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C179" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C180" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C181" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C182" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C183" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C184" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C185" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C186" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C187" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C189" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="190" spans="3:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="C190" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="191" spans="3:3" ht="16" x14ac:dyDescent="0.35">
+      <c r="C191" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E923B1D1-7D72-4557-90B4-95DCE7CFCEFB}">
   <dimension ref="C4:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
